--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571260448</v>
+        <v>46157.93108332413</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108332413</v>
+        <v>46157.93177929959</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93177929959</v>
+        <v>46157.93402819736</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93402819736</v>
+        <v>46157.93720795352</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93720795352</v>
+        <v>46158.28218866231</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28218866231</v>
+        <v>46158.2969315463</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2969315463</v>
+        <v>46158.29817944324</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29817944324</v>
+        <v>46158.33389830674</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33389830674</v>
+        <v>46158.36859683627</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36859683627</v>
+        <v>46158.37290282128</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
